--- a/UTCUTS/A1_Outputs/reference_freeze/A-O_Demand.xlsx
+++ b/UTCUTS/A1_Outputs/reference_freeze/A-O_Demand.xlsx
@@ -9116,7 +9116,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41237A3-81A5-4615-826F-6E4CBB82AEF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2647DF0-1FE7-4F02-9362-59BB6470197A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
